--- a/artfynd/A 8302-2025 artfynd.xlsx
+++ b/artfynd/A 8302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,118 +784,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>87563377</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Vattukärret, Vb</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>792739.1319886288</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7233232.956567733</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Byske</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
